--- a/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 2,43</t>
+          <t>-4,65; 2,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 5,13</t>
+          <t>-3,08; 5,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 6,61</t>
+          <t>-3,41; 6,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 5,27</t>
+          <t>-2,57; 5,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,1; 240,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 583,42</t>
+          <t>-95,22; 744,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-69,7; 494,58</t>
+          <t>-63,64; 453,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,54; 295,59</t>
+          <t>-55,05; 321,91</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,04</t>
+          <t>-1,79; 4,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,23</t>
+          <t>-0,35; 3,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 3,24</t>
+          <t>-4,2; 2,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 2,3</t>
+          <t>-5,29; 1,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,84; 551,32</t>
+          <t>-81,58; 568,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,38; 108,51</t>
+          <t>-65,62; 99,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,67; 71,3</t>
+          <t>-66,77; 58,07</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 1,48</t>
+          <t>-6,13; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,76</t>
+          <t>-1,41; 4,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 6,9</t>
+          <t>-1,96; 7,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 2,8</t>
+          <t>-5,86; 3,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-89,28; 80,82</t>
+          <t>-90,18; 105,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-80,37; 1029,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 316,87</t>
+          <t>-37,63; 329,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-64,62; 60,61</t>
+          <t>-63,61; 73,54</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,1</t>
+          <t>-2,99; 1,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 6,29</t>
+          <t>-0,3; 5,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,88</t>
+          <t>-5,75; 2,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 4,91</t>
+          <t>-4,44; 5,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,48; 325,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 1397,51</t>
+          <t>-47,11; 1439,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 84,47</t>
+          <t>-68,25; 94,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 115,37</t>
+          <t>-48,86; 111,52</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,87</t>
+          <t>-2,13; 0,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,37</t>
+          <t>0,07; 3,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,26</t>
+          <t>-1,83; 2,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,79</t>
+          <t>-2,48; 1,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 50,99</t>
+          <t>-60,02; 51,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 423,77</t>
+          <t>-5,64; 386,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 59,16</t>
+          <t>-31,89; 69,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 38,48</t>
+          <t>-36,51; 33,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,34</t>
+          <t>-4,66; 2,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 5,18</t>
+          <t>-2,71; 5,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 6,43</t>
+          <t>-4,02; 6,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 5,46</t>
+          <t>-2,49; 5,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-87,1; 240,63</t>
+          <t>-88,13; 244,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-95,22; 744,79</t>
+          <t>-79,58; 554,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,64; 453,51</t>
+          <t>-62,39; 515,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,05; 321,91</t>
+          <t>-56,94; 295,83</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 4,12</t>
+          <t>-1,89; 3,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,6</t>
+          <t>-0,42; 3,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 2,85</t>
+          <t>-4,36; 2,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 1,99</t>
+          <t>-4,31; 2,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,58; 568,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,62; 99,35</t>
+          <t>-64,91; 95,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,77; 58,07</t>
+          <t>-62,14; 64,43</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 1,51</t>
+          <t>-5,83; 1,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,94</t>
+          <t>-1,23; 5,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 7,0</t>
+          <t>-1,78; 7,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 3,05</t>
+          <t>-5,81; 3,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-90,18; 105,22</t>
+          <t>-89,36; 100,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,92; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-37,63; 329,37</t>
+          <t>-34,96; 313,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,61; 73,54</t>
+          <t>-66,68; 69,04</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,98</t>
+          <t>-3,01; 1,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,9</t>
+          <t>-0,1; 6,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,61</t>
+          <t>-5,54; 2,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 5,07</t>
+          <t>-4,84; 4,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,54; 307,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,11; 1439,77</t>
+          <t>-36,16; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,25; 94,97</t>
+          <t>-70,64; 80,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,86; 111,52</t>
+          <t>-52,98; 109,8</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,93</t>
+          <t>-2,07; 1,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,22</t>
+          <t>0,19; 3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,56</t>
+          <t>-1,99; 2,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,6</t>
+          <t>-2,28; 1,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 51,67</t>
+          <t>-60,37; 56,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 386,7</t>
+          <t>2,47; 391,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 69,55</t>
+          <t>-34,43; 66,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,51; 33,81</t>
+          <t>-33,39; 41,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,49</t>
+          <t>-4,54; 2,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 5,04</t>
+          <t>-3,03; 5,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 6,68</t>
+          <t>-3,78; 6,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,51</t>
+          <t>-3,38; 5,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-88,13; 244,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,58; 554,47</t>
+          <t>-100,0; 583,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,39; 515,74</t>
+          <t>-69,7; 494,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,94; 295,83</t>
+          <t>-61,4; 272,37</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-1,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-21,67%</t>
+          <t>-21,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,82</t>
+          <t>-1,82; 4,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,51</t>
+          <t>-0,42; 3,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 2,87</t>
+          <t>-4,42; 3,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,48</t>
+          <t>-5,35; 2,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>-78,84; 551,32</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 95,98</t>
+          <t>-64,38; 108,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,14; 64,43</t>
+          <t>-66,04; 73,57</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-22,43%</t>
+          <t>-4,54%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,5</t>
+          <t>-5,41; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,47</t>
+          <t>-1,41; 4,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 7,34</t>
+          <t>-2,21; 6,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 3,29</t>
+          <t>-4,74; 4,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-89,36; 100,6</t>
+          <t>-89,28; 80,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,92; —</t>
+          <t>-80,37; 1029,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 313,29</t>
+          <t>-41,66; 316,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 69,04</t>
+          <t>-56,38; 100,68</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,84</t>
+          <t>-3,0; 2,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 6,63</t>
+          <t>-0,1; 6,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 2,87</t>
+          <t>-5,4; 2,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,92</t>
+          <t>-5,49; 5,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,54; 307,57</t>
+          <t>-86,48; 325,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,16; —</t>
+          <t>-51,13; 1397,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,64; 80,63</t>
+          <t>-70,37; 84,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 109,8</t>
+          <t>-54,69; 119,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,94%</t>
+          <t>-1,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,03</t>
+          <t>-2,11; 0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,32</t>
+          <t>0,19; 3,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,5</t>
+          <t>-1,92; 2,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,9</t>
+          <t>-2,39; 2,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 56,46</t>
+          <t>-59,06; 50,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 391,45</t>
+          <t>3,81; 423,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 66,33</t>
+          <t>-32,91; 59,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,39; 41,64</t>
+          <t>-33,13; 43,22</t>
         </is>
       </c>
     </row>
